--- a/docs/herramientas-mx/plan_maestro.xlsx
+++ b/docs/herramientas-mx/plan_maestro.xlsx
@@ -603,14 +603,14 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26254.73</v>
+        <v>26544.79</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>26254.73</v>
+        <v>26544.79</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>76,258 si nada del listado aparece</t>
+          <t>76,548 si nada del listado aparece</t>
         </is>
       </c>
     </row>
@@ -656,14 +656,14 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>99679.78999999999</v>
+        <v>100127.53</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>125934.52</v>
+        <v>126672.32</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>148,053 si nada del listado aparece</t>
+          <t>148,501 si nada del listado aparece</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>125934.52</v>
+        <v>126672.32</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
@@ -762,14 +762,14 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>190995.21</v>
+        <v>193083.27</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>316929.73</v>
+        <v>319755.59</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>216,765 si nada del listado aparece; RFID aparte 20,076</t>
+          <t>218,853 si nada del listado aparece; RFID aparte 20,076</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>316929.73</v>
+        <v>319755.59</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
@@ -913,22 +913,22 @@
         <v>6407.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>13197</v>
+        <v>13895</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>813.55</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5837.06</v>
+        <v>5429.12</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>26254.73</v>
+        <v>26544.79</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>76257.74000000001</v>
+        <v>76547.8</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26254.73</v>
+        <v>26544.79</v>
       </c>
     </row>
     <row r="3">
@@ -946,22 +946,22 @@
         <v>57641.73</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>29638</v>
+        <v>31034</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>1508.1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>10891.96</v>
+        <v>9943.700000000001</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>99679.78999999999</v>
+        <v>100127.53</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>148053.23</v>
+        <v>148500.97</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>125934.52</v>
+        <v>126672.32</v>
       </c>
     </row>
     <row r="4">
@@ -979,22 +979,22 @@
         <v>102373.25</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>65003</v>
+        <v>66399</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>3035.65</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>20583.31</v>
+        <v>21275.37</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>190995.21</v>
+        <v>193083.27</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>216764.51</v>
+        <v>218852.57</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>316929.73</v>
+        <v>319755.59</v>
       </c>
     </row>
     <row r="5">
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>267787.84</v>
+        <v>270461.88</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>51.01</v>
+        <v>50.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2574.6</v>
+        <v>2555.7</v>
       </c>
     </row>
     <row r="3">
@@ -1097,13 +1097,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>475850.48</v>
+        <v>481421.12</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>78.05</v>
+        <v>82.44</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3940</v>
+        <v>4144.6</v>
       </c>
     </row>
     <row r="4">
@@ -1116,13 +1116,13 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>316929.73</v>
+        <v>319755.59</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>58.95</v>
+        <v>57.9</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2974.7</v>
+        <v>2911.2</v>
       </c>
     </row>
     <row r="5">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>614037.29</v>
+        <v>621000.59</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>97.56</v>
+        <v>103.05</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4925</v>
+        <v>5180.7</v>
       </c>
     </row>
     <row r="6">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>366071.62</v>
+        <v>369049.31</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>66.88</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3374.9</v>
+        <v>3266.8</v>
       </c>
     </row>
     <row r="7">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>752224.11</v>
+        <v>760580.0699999999</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>117.07</v>
+        <v>123.66</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5910</v>
+        <v>6216.9</v>
       </c>
     </row>
   </sheetData>
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>465.2</v>
+        <v>431.3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1.1</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>17.21</v>
+        <v>15.71</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>868.2</v>
+        <v>790.1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>10.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>32.52</v>
+        <v>33.61</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1641.3</v>
+        <v>1689.8</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>20.1</v>
+        <v>20.7</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
